--- a/documents/CRR_Test_Case_Results_Matrix_v2.xlsx
+++ b/documents/CRR_Test_Case_Results_Matrix_v2.xlsx
@@ -2787,7 +2787,7 @@
         <v>v2.3.0: ⚠ Sonnet4 FABRICATES | ✓ Sonnet4.6 correct</v>
       </c>
       <c r="S37" t="str">
-        <v>⚠ CRITICAL SAFETY FINDING: Sonnet4 fabrication confirmed. Sonnet4.6 resolves.</v>
+        <v>⚠ CRITICAL SAFETY FINDING: Sonnet4 fabrication confirmed. FABRICATION PERSISTS ON SONNET 4.6 — REG02-B (22 Jun 2026): 'no focal pathology' present in met_criteria, verdict proceeds 3/3 (expected at_risk). The earlier 'Sonnet4.6 resolves' note reflected Sonnet-4-vs-4.6 comparison testing, not resolution on the current suite. Exam-type routing gap (CT Other/us_fna_biopsy invisible pre-switch) also remains — TA-SRC-01 §9 Category A.</v>
       </c>
       <c r="T37" t="str">
         <v>⚠ Sonnet4 stated "No focal pathology" when note explicitly documents "15cm epigastric mass". Direct clinical contradiction. Sonnet4.6 consistent across all runs. This is the primary model selection safety criterion.</v>
@@ -5962,7 +5962,7 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>Cross-run divergence between REG02-B (22 Jun: declined ×3) and baseline (12 Jul: at_risk ×3) under nominally identical config — environment/model drift, not switch-attributable; baseline (12 Jul) is the sole comparator for the post-switch diff.</v>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -6915,7 +6915,7 @@
         <v/>
       </c>
       <c r="Q24" t="str">
-        <v/>
+        <v>Cross-run divergence between REG02-B (22 Jun: at_risk ×3) and baseline (12 Jul: declined ×3) under nominally identical config — environment/model drift, not switch-attributable; baseline (12 Jul) is the sole comparator for the post-switch diff.</v>
       </c>
       <c r="R24" t="str">
         <v/>
@@ -8138,7 +8138,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8720,9 +8720,69 @@
         <v>2026-07-12</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>INT-002</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Current Status (Test Case Results)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>⚠ CRITICAL SAFETY FINDING: Sonnet4 fabrication confirmed. Sonnet4.6 resolves.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>⚠ CRITICAL SAFETY FINDING: Sonnet4 fabrication confirmed. FABRICATION PERSISTS ON SONNET 4.6 — REG02-B (22 Jun 2026): 'no focal pathology' present in met_criteria, verdict proceeds 3/3 (expected at_risk). The earlier 'Sonnet4.6 resolves' note reflected Sonnet-4-vs-4.6 comparison testing, not resolution on the current suite. Exam-type routing gap (CT Other/us_fna_biopsy invisible pre-switch) also remains — TA-SRC-01 §9 Category A.</v>
+      </c>
+      <c r="E30" t="str">
+        <v>instructions/prompt-v3-phase0-audit.md §2; scripts/reg02-results.json</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-07-12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>DG-003</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Stability / Quality Notes (Structured Re-Eval)</v>
+      </c>
+      <c r="C31" t="str">
+        <v>(blank)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Cross-run divergence between REG02-B (22 Jun: declined ×3) and baseline (12 Jul: at_risk ×3) under nominally identical config — environment/model drift, not switch-attributable; baseline (12 Jul) is the sole comparator for the post-switch diff.</v>
+      </c>
+      <c r="E31" t="str">
+        <v>scripts/reg02-results.json; scripts/reg_baseline_ta-src-01_20260712_01-results.json</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-07-12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>INT-001</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Stability / Quality Notes (Structured Re-Eval)</v>
+      </c>
+      <c r="C32" t="str">
+        <v>(blank)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Cross-run divergence between REG02-B (22 Jun: at_risk ×3) and baseline (12 Jul: declined ×3) under nominally identical config — environment/model drift, not switch-attributable; baseline (12 Jul) is the sole comparator for the post-switch diff.</v>
+      </c>
+      <c r="E32" t="str">
+        <v>scripts/reg02-results.json; scripts/reg_baseline_ta-src-01_20260712_01-results.json</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-07-12</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F32"/>
   </ignoredErrors>
 </worksheet>
 </file>